--- a/anti-amyloid-npi-analysis/output/抄録D_背景と結果の表.xlsx
+++ b/anti-amyloid-npi-analysis/output/抄録D_背景と結果の表.xlsx
@@ -9,8 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table1_背景と認知機能" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table2_比率の比較" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="患者背景_連結不可能化" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table1_背景と認知機能'!$A$1:$I$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Table2_比率の比較'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'患者背景_連結不可能化'!$A$1:$E$98</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -438,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.8" customWidth="1" min="1" max="1"/>
@@ -507,12 +512,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ベースライン MMSE合計（点）</t>
+          <t>年齢（歳）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>24.9±2.0</t>
+          <t>74.8±4.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -522,7 +527,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.5±0.7</t>
+          <t>78.0±4.2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -532,17 +537,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23, 22</t>
+          <t>75, 81</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.13186813186813187</t>
+          <t>0.5494505494505495</t>
         </is>
       </c>
     </row>
@@ -554,12 +559,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ベースライン CDR-SB（点）</t>
+          <t>ベースライン MMSE合計（点）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.5±0.7</t>
+          <t>24.9±2.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -569,7 +574,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.8±0.4</t>
+          <t>22.5±0.7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -579,17 +584,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2, 1.5</t>
+          <t>23, 22</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.7912087912087913</t>
+          <t>0.13186813186813187</t>
         </is>
       </c>
     </row>
@@ -601,12 +606,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ベースライン Global CDR</t>
+          <t>ベースライン CDR-SB（点）</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.50±0.00</t>
+          <t>1.5±0.7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -616,7 +621,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.50±0.00</t>
+          <t>1.8±0.4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -626,15 +631,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.5, 0.5</t>
+          <t>2, 1.5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.7912087912087913</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -644,44 +653,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ベースライン MoCA-J（点）</t>
+          <t>ベースライン Global CDR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21.6±1.9</t>
+          <t>0.50±0.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>0.50±0.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0.5, 0.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.3333333333333333</t>
-        </is>
-      </c>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -691,42 +696,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ベースライン MMSE時間見当識（点）</t>
+          <t>ベースライン MoCA-J（点）</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.2±1.0</t>
+          <t>21.6±1.9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.0±0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2, 2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0.02197802197802198</t>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.3333333333333333</t>
         </is>
       </c>
     </row>
@@ -738,89 +743,89 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>観察期間（か月）</t>
+          <t>ベースライン MMSE時間見当識（点）</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11.7±4.6</t>
+          <t>4.2±1.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>2.0±0.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>2, 2</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.5454545454545454</t>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0.02197802197802198</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>追跡時</t>
+          <t>患者背景</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>追跡時 MMSE合計（点）</t>
+          <t>観察期間（か月）</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>24.4±2.3</t>
+          <t>11.7±4.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.0±1.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>23, 25</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.9230769230769231</t>
+          <t>0.5454545454545454</t>
         </is>
       </c>
     </row>
@@ -832,12 +837,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>追跡時 CDR-SB（点）</t>
+          <t>追跡時 MMSE合計（点）</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.5±1.1</t>
+          <t>24.4±2.3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -847,7 +852,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.8±1.8</t>
+          <t>24.0±1.4</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -857,17 +862,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4, 1.5</t>
+          <t>23, 25</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9230769230769231</t>
         </is>
       </c>
     </row>
@@ -879,12 +884,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>追跡時 MMSE時間見当識（点）</t>
+          <t>追跡時 CDR-SB（点）</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.4±1.5</t>
+          <t>2.5±1.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.5±0.7</t>
+          <t>2.8±1.8</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -904,34 +909,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3, 4</t>
+          <t>4, 1.5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.9230769230769231</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>変化量</t>
+          <t>追跡時</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ΔMMSE合計（点）</t>
+          <t>追跡時 MMSE時間見当識（点）</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.5±1.9</t>
+          <t>3.4±1.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -941,7 +946,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5±2.1</t>
+          <t>3.5±0.7</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -951,17 +956,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0, 3</t>
+          <t>3, 4</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.3516483516483517</t>
+          <t>0.9230769230769231</t>
         </is>
       </c>
     </row>
@@ -973,12 +978,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ΔCDR-SB（点）</t>
+          <t>ΔMMSE合計（点）</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.9±0.8</t>
+          <t>-0.5±1.9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -988,7 +993,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.0±1.4</t>
+          <t>1.5±2.1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -998,17 +1003,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2, 0</t>
+          <t>0, 3</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3516483516483517</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1025,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ΔGlobal CDR</t>
+          <t>ΔCDR-SB（点）</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.08±0.19</t>
+          <t>0.9±0.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1035,7 +1040,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.25±0.35</t>
+          <t>1.0±1.4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1045,17 +1050,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.5, 0</t>
+          <t>2, 0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.5494505494505495</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1072,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ΔMMSE時間見当識（点）</t>
+          <t>ΔGlobal CDR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.8±0.8</t>
+          <t>0.08±0.19</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1082,7 +1087,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5±0.7</t>
+          <t>0.25±0.35</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1092,34 +1097,34 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1, 2</t>
+          <t>0.5, 0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0.02197802197802198</t>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.5494505494505495</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>変化量（MMSE他下位項目）</t>
+          <t>変化量</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ΔMMSE 場所見当識（点）</t>
+          <t>ΔMMSE時間見当識（点）</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.2±0.7</t>
+          <t>-0.8±0.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1129,7 +1134,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.5±0.7</t>
+          <t>1.5±0.7</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1139,17 +1144,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0, 1</t>
+          <t>1, 2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.5494505494505495</t>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0.02197802197802198</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1166,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ΔMMSE 物品呼称（点）</t>
+          <t>ΔMMSE 場所見当識（点）</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0±0.0</t>
+          <t>0.2±0.7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1176,7 +1181,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.0±0.0</t>
+          <t>0.5±0.7</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1186,7 +1191,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0, 0</t>
+          <t>0, 1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1199,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.5494505494505495</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1204,12 +1213,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ΔMMSE 記銘（点）</t>
+          <t>ΔMMSE 物品呼称（点）</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.2±0.4</t>
+          <t>0.0±0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1237,11 +1246,7 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.7912087912087913</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1251,12 +1256,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ΔMMSE 注意計算（点）</t>
+          <t>ΔMMSE 記銘（点）</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.2±1.3</t>
+          <t>0.2±0.4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1266,7 +1271,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-0.5±2.1</t>
+          <t>0.0±0.0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1276,7 +1281,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2, 1</t>
+          <t>0, 0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1286,7 +1291,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.9230769230769231</t>
+          <t>0.7912087912087913</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1303,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ΔMMSE 遅延再生（点）</t>
+          <t>ΔMMSE 注意計算（点）</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.2±0.5</t>
+          <t>0.2±1.3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1313,7 +1318,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-0.5±0.7</t>
+          <t>-0.5±2.1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1323,7 +1328,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0, -1</t>
+          <t>-2, 1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1333,7 +1338,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.6593406593406594</t>
+          <t>0.9230769230769231</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1350,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ΔMMSE 復唱（点）</t>
+          <t>ΔMMSE 遅延再生（点）</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.1±0.3</t>
+          <t>-0.2±0.5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1360,7 +1365,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0±0.0</t>
+          <t>-0.5±0.7</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1370,7 +1375,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0, 0</t>
+          <t>0, -1</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1380,7 +1385,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.9230769230769231</t>
+          <t>0.6593406593406594</t>
         </is>
       </c>
     </row>
@@ -1392,24 +1397,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ΔMMSE 読字理解（点）</t>
+          <t>ΔMMSE 復唱（点）</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>0.1±0.3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>0.0±0.0</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0.0±0.0</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>2</t>
@@ -1425,7 +1430,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.9230769230769231</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1435,7 +1444,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ΔMMSE 3段階命令（点）</t>
+          <t>ΔMMSE 読字理解（点）</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1478,7 +1487,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ΔMMSE 書字（点）</t>
+          <t>ΔMMSE 3段階命令（点）</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1521,7 +1530,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ΔMMSE 図形模写（点）</t>
+          <t>ΔMMSE 書字（点）</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1536,7 +1545,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.5±0.7</t>
+          <t>0.0±0.0</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1546,7 +1555,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1, 0</t>
+          <t>0, 0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1554,26 +1563,22 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.3516483516483517</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>変化量（CDR下位領域）</t>
+          <t>変化量（MMSE他下位項目）</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ΔCDR 記憶（点）</t>
+          <t>ΔMMSE 図形模写（点）</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.17±0.25</t>
+          <t>0.0±0.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1583,7 +1588,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.25±0.35</t>
+          <t>0.5±0.7</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1593,7 +1598,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.5, 0</t>
+          <t>1, 0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1603,7 +1608,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.7912087912087913</t>
+          <t>0.3516483516483517</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1620,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ΔCDR 見当識（点）</t>
+          <t>ΔCDR 記憶（点）</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.25±0.26</t>
+          <t>0.17±0.25</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1630,7 +1635,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.00±0.00</t>
+          <t>0.25±0.35</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1640,17 +1645,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0, 0</t>
+          <t>0.5, 0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.3516483516483517</t>
+          <t>0.7912087912087913</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1667,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ΔCDR 判断力・問題解決（点）</t>
+          <t>ΔCDR 見当識（点）</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.04±0.14</t>
+          <t>0.25±0.26</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1677,7 +1682,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.25±0.35</t>
+          <t>0.00±0.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1687,17 +1692,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.5, 0</t>
+          <t>0, 0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.4395604395604396</t>
+          <t>0.3516483516483517</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1714,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ΔCDR 地域社会の活動（点）</t>
+          <t>ΔCDR 判断力・問題解決（点）</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.17±0.25</t>
+          <t>0.04±0.14</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1744,7 +1749,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.7912087912087913</t>
+          <t>0.4395604395604396</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1761,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ΔCDR 家庭・趣味（点）</t>
+          <t>ΔCDR 地域社会の活動（点）</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.21±0.33</t>
+          <t>0.17±0.25</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1791,7 +1796,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.9230769230769231</t>
+          <t>0.7912087912087913</t>
         </is>
       </c>
     </row>
@@ -1803,46 +1808,94 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>ΔCDR 家庭・趣味（点）</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.21±0.33</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.25±0.35</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.5, 0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.9230769230769231</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>変化量（CDR下位領域）</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>ΔCDR 身の回りの世話（点）</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>0.08±0.29</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>0.00±0.00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>0, 0</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>0.9230769230769231</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1853,7 +1906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.6" customWidth="1" min="1" max="1"/>
@@ -1899,81 +1952,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ベースラインで易怒性あり</t>
+          <t>女性</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>7/12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5054945054945055</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>追跡時に易怒性あり</t>
+          <t>ベースラインで易怒性あり</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>3/12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.4725274725274725</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>易怒性が新規出現（なし→あり）</t>
+          <t>追跡時に易怒性あり</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>6/12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1988,24 +2041,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.1648351648351648</t>
+          <t>0.4725274725274725</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MMSE時間見当識が改善（Δ≧+1）</t>
+          <t>易怒性が新規出現（なし→あり）</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0/12</t>
+          <t>4/12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2018,58 +2071,58 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0.010989010989010988</t>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.1648351648351648</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MMSE時間見当識が低下（Δ≦−1）</t>
+          <t>MMSE時間見当識が改善（Δ≧+1）</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>0/12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.16483516483516483</t>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0.010989010989010988</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MMSE合計が低下（Δ≦−1）</t>
+          <t>MMSE時間見当識が低下（Δ≦−1）</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>8/12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2084,43 +2137,2480 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.4725274725274724</t>
+          <t>0.16483516483516483</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>MMSE合計が低下（Δ≦−1）</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.4725274725274724</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>CDR-SBが悪化（Δ≧+0.5）</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>9/12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.5054945054945055</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E98"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>研究番号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>薬剤</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>年齢</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>投与開始日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2024-02-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>レカネマブ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>男性</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.5054945054945055</t>
-        </is>
-      </c>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>L13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>L15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>L16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>L17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>L18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>L21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>L22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>L24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>L27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>L28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>L29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>L31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>L32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>L33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>L34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2024-01-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>L35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>L36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>L37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>L38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>L39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2025-01-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>L41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>L42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>L43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>L44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>L45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>L46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>L47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>L48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>L49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>L50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>L51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>L52</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>L53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>L54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>L55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>L56</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>L57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>L58</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>L59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>L60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>L61</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>L62</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>L63</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>L64</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>L65</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>L66</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>レカネマブ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>D18</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>D19</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>D21</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>D24</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>D25</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>D26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>D27</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>D28</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>D29</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>D30</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>女性</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>D31</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ドナネマブ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>